--- a/testbuild/StructureDefinition-no-basis-Patient.xlsx
+++ b/testbuild/StructureDefinition-no-basis-Patient.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4046" uniqueCount="602">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4046" uniqueCount="599">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.3-test</t>
+    <t>2.2.4-test</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -464,25 +464,29 @@
     <t>The citizenship of the patient. should be a country code from ISO 3166 code system</t>
   </si>
   <si>
-    <t>Patient.extension:citizenship.id</t>
-  </si>
-  <si>
-    <t>Patient.extension.id</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
     <t xml:space="preserve">ele-1
 </t>
   </si>
   <si>
+    <t>Patient.extension:citizenship.id</t>
+  </si>
+  <si>
+    <t>Patient.extension.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
     <t>n/a</t>
   </si>
   <si>
@@ -499,7 +503,7 @@
     <t>Additional content defined by implementations</t>
   </si>
   <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
@@ -564,20 +568,13 @@
     <t>Value of extension</t>
   </si>
   <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R5/extensibility.html) for a list).</t>
-  </si>
-  <si>
-    <t>example</t>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
   </si>
   <si>
     <t>urn:iso:std:iso:3166</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ext-1
-</t>
   </si>
   <si>
     <t>Patient.extension:citizenship.extension:period</t>
@@ -624,7 +621,7 @@
   </si>
   <si>
     <t>base64Binary
-booleancanonicalcodedatedateTimedecimalidinstantintegermarkdownoidpositiveIntstringtimeunsignedInturiurluuidAddressAgeAnnotationAttachmentCodeableConceptCodingContactPointCountDistanceDurationHumanNameIdentifierMoneyPeriodQuantityRangeRatioReferenceSampledDataSignatureTimingContactDetailDataRequirementExpressionParameterDefinitionRelatedArtifactTriggerDefinitionUsageContextDosageMeta</t>
+booleancanonicalcodedatedateTimedecimalidinstantintegermarkdownoidpositiveIntstringtimeunsignedInturiurluuidAddressAgeAnnotationAttachmentCodeableConceptCodingContactPointCountDistanceDurationHumanNameIdentifierMoneyPeriodQuantityRangeRatioReferenceSampledDataSignatureTimingContactDetailContributorDataRequirementExpressionParameterDefinitionRelatedArtifactTriggerDefinitionUsageContextDosageMeta</t>
   </si>
   <si>
     <t>Patient.modifierExtension</t>
@@ -694,17 +691,10 @@
     <t>Patient.identifier.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
     <t>Patient.identifier:FNR.extension</t>
   </si>
   <si>
     <t>Patient.identifier.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
     <t>Patient.identifier:FNR.use</t>
@@ -3366,7 +3356,7 @@
         <v>77</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>78</v>
+        <v>144</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>137</v>
@@ -3389,10 +3379,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3415,13 +3405,13 @@
         <v>78</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>88</v>
+        <v>147</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -3472,7 +3462,7 @@
         <v>78</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>76</v>
@@ -3481,13 +3471,13 @@
         <v>86</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>149</v>
+        <v>78</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AL11" t="s" s="2">
         <v>78</v>
@@ -3504,14 +3494,14 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -3533,13 +3523,13 @@
         <v>131</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3580,7 +3570,7 @@
         <v>134</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AD12" t="s" s="2">
         <v>78</v>
@@ -3589,7 +3579,7 @@
         <v>135</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>76</v>
@@ -3604,7 +3594,7 @@
         <v>137</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>78</v>
@@ -3621,13 +3611,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D13" t="s" s="2">
         <v>78</v>
@@ -3655,7 +3645,7 @@
         <v>132</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -3706,7 +3696,7 @@
         <v>78</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>76</v>
@@ -3738,10 +3728,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3764,13 +3754,13 @@
         <v>78</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>88</v>
+        <v>147</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3821,7 +3811,7 @@
         <v>78</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>76</v>
@@ -3830,13 +3820,13 @@
         <v>86</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>149</v>
+        <v>78</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>78</v>
@@ -3853,10 +3843,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3927,7 +3917,7 @@
         <v>134</v>
       </c>
       <c r="AC15" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AD15" t="s" s="2">
         <v>78</v>
@@ -3936,7 +3926,7 @@
         <v>135</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>76</v>
@@ -3968,10 +3958,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3997,13 +3987,13 @@
         <v>100</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4011,7 +4001,7 @@
       </c>
       <c r="Q16" s="2"/>
       <c r="R16" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="S16" t="s" s="2">
         <v>78</v>
@@ -4053,7 +4043,7 @@
         <v>78</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>86</v>
@@ -4085,10 +4075,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4111,13 +4101,13 @@
         <v>78</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4144,7 +4134,7 @@
         <v>78</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>177</v>
+        <v>110</v>
       </c>
       <c r="Y17" s="2"/>
       <c r="Z17" t="s" s="2">
@@ -4175,7 +4165,7 @@
         <v>86</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>180</v>
+        <v>78</v>
       </c>
       <c r="AJ17" t="s" s="2">
         <v>98</v>
@@ -4198,13 +4188,13 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="C18" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="B18" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="C18" t="s" s="2">
-        <v>182</v>
       </c>
       <c r="D18" t="s" s="2">
         <v>78</v>
@@ -4229,10 +4219,10 @@
         <v>131</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>183</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>184</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4283,7 +4273,7 @@
         <v>78</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>76</v>
@@ -4315,10 +4305,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4341,13 +4331,13 @@
         <v>78</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>88</v>
+        <v>147</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4398,7 +4388,7 @@
         <v>78</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>76</v>
@@ -4407,13 +4397,13 @@
         <v>86</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>149</v>
+        <v>78</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>78</v>
@@ -4430,10 +4420,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4504,7 +4494,7 @@
         <v>134</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>78</v>
@@ -4513,7 +4503,7 @@
         <v>135</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>76</v>
@@ -4545,10 +4535,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4574,13 +4564,13 @@
         <v>100</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4588,7 +4578,7 @@
       </c>
       <c r="Q21" s="2"/>
       <c r="R21" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="S21" t="s" s="2">
         <v>78</v>
@@ -4630,7 +4620,7 @@
         <v>78</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>86</v>
@@ -4662,10 +4652,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4688,13 +4678,13 @@
         <v>78</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4754,7 +4744,7 @@
         <v>86</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>180</v>
+        <v>78</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>98</v>
@@ -4777,10 +4767,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="B23" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="B23" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4806,13 +4796,13 @@
         <v>100</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4820,7 +4810,7 @@
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="S23" t="s" s="2">
         <v>78</v>
@@ -4862,7 +4852,7 @@
         <v>78</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>86</v>
@@ -4894,10 +4884,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="B24" t="s" s="2">
         <v>193</v>
-      </c>
-      <c r="B24" t="s" s="2">
-        <v>194</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4920,13 +4910,13 @@
         <v>78</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4986,7 +4976,7 @@
         <v>86</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>180</v>
+        <v>78</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>98</v>
@@ -5009,14 +4999,14 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -5038,16 +5028,16 @@
         <v>131</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="O25" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>78</v>
@@ -5096,7 +5086,7 @@
         <v>78</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>76</v>
@@ -5128,10 +5118,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5154,17 +5144,17 @@
         <v>87</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="M26" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>204</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>78</v>
@@ -5201,7 +5191,7 @@
         <v>78</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AC26" s="2"/>
       <c r="AD26" t="s" s="2">
@@ -5211,7 +5201,7 @@
         <v>135</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>76</v>
@@ -5226,16 +5216,16 @@
         <v>98</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="AL26" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="AL26" t="s" s="2">
+      <c r="AM26" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="AM26" t="s" s="2">
+      <c r="AN26" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>210</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>78</v>
@@ -5243,13 +5233,13 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="C27" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="B27" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="C27" t="s" s="2">
-        <v>212</v>
       </c>
       <c r="D27" t="s" s="2">
         <v>78</v>
@@ -5271,17 +5261,17 @@
         <v>87</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>213</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>214</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>78</v>
@@ -5330,7 +5320,7 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>76</v>
@@ -5345,16 +5335,16 @@
         <v>98</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="AL27" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="AL27" t="s" s="2">
+      <c r="AM27" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="AM27" t="s" s="2">
+      <c r="AN27" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>210</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>78</v>
@@ -5362,10 +5352,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="B28" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="B28" t="s" s="2">
-        <v>216</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5388,13 +5378,13 @@
         <v>78</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>217</v>
+        <v>147</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5445,7 +5435,7 @@
         <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>76</v>
@@ -5460,7 +5450,7 @@
         <v>78</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>78</v>
@@ -5477,14 +5467,14 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5506,13 +5496,13 @@
         <v>131</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>220</v>
+        <v>156</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5553,7 +5543,7 @@
         <v>134</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>78</v>
@@ -5562,7 +5552,7 @@
         <v>135</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
@@ -5577,7 +5567,7 @@
         <v>137</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>78</v>
@@ -5594,10 +5584,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5623,16 +5613,16 @@
         <v>106</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="O30" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>78</v>
@@ -5657,31 +5647,31 @@
         <v>78</v>
       </c>
       <c r="X30" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="Z30" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF30" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="Y30" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="Z30" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="AA30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF30" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
@@ -5696,7 +5686,7 @@
         <v>98</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>78</v>
@@ -5713,10 +5703,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5739,19 +5729,19 @@
         <v>87</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="M31" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="O31" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>78</v>
@@ -5776,31 +5766,31 @@
         <v>78</v>
       </c>
       <c r="X31" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="Y31" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="Z31" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="AA31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF31" t="s" s="2">
         <v>238</v>
-      </c>
-      <c r="Y31" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="Z31" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="AA31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF31" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
@@ -5815,7 +5805,7 @@
         <v>98</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>78</v>
@@ -5824,7 +5814,7 @@
         <v>78</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>78</v>
@@ -5832,10 +5822,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5861,29 +5851,29 @@
         <v>100</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="O32" t="s" s="2">
         <v>245</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>248</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="S32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="T32" t="s" s="2">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="U32" t="s" s="2">
         <v>78</v>
@@ -5919,7 +5909,7 @@
         <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>76</v>
@@ -5934,7 +5924,7 @@
         <v>98</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>78</v>
@@ -5943,7 +5933,7 @@
         <v>78</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>78</v>
@@ -5951,14 +5941,14 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5977,16 +5967,16 @@
         <v>87</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>217</v>
+        <v>147</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -6000,7 +5990,7 @@
         <v>78</v>
       </c>
       <c r="T33" t="s" s="2">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="U33" t="s" s="2">
         <v>78</v>
@@ -6036,7 +6026,7 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>76</v>
@@ -6051,7 +6041,7 @@
         <v>98</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>78</v>
@@ -6060,7 +6050,7 @@
         <v>78</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>78</v>
@@ -6068,10 +6058,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6094,13 +6084,13 @@
         <v>87</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6151,7 +6141,7 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>76</v>
@@ -6166,7 +6156,7 @@
         <v>98</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>78</v>
@@ -6175,7 +6165,7 @@
         <v>78</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>78</v>
@@ -6183,10 +6173,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6209,16 +6199,16 @@
         <v>87</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="L35" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="N35" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="L35" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6268,7 +6258,7 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>76</v>
@@ -6283,7 +6273,7 @@
         <v>98</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>78</v>
@@ -6292,7 +6282,7 @@
         <v>78</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>78</v>
@@ -6300,13 +6290,13 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="D36" t="s" s="2">
         <v>78</v>
@@ -6328,17 +6318,17 @@
         <v>87</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>78</v>
@@ -6387,7 +6377,7 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
@@ -6402,16 +6392,16 @@
         <v>98</v>
       </c>
       <c r="AK36" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="AL36" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="AL36" t="s" s="2">
+      <c r="AM36" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="AM36" t="s" s="2">
+      <c r="AN36" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>210</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>78</v>
@@ -6419,10 +6409,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6445,13 +6435,13 @@
         <v>78</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>217</v>
+        <v>147</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6502,7 +6492,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
@@ -6517,7 +6507,7 @@
         <v>78</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>78</v>
@@ -6534,14 +6524,14 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6563,13 +6553,13 @@
         <v>131</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>220</v>
+        <v>156</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6610,7 +6600,7 @@
         <v>134</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>78</v>
@@ -6619,7 +6609,7 @@
         <v>135</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>76</v>
@@ -6634,7 +6624,7 @@
         <v>137</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>78</v>
@@ -6651,10 +6641,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6680,16 +6670,16 @@
         <v>106</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="O39" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>78</v>
@@ -6714,31 +6704,31 @@
         <v>78</v>
       </c>
       <c r="X39" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="Z39" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF39" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="Y39" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="Z39" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="AA39" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB39" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC39" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD39" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE39" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF39" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>76</v>
@@ -6753,7 +6743,7 @@
         <v>98</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>78</v>
@@ -6770,10 +6760,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6796,19 +6786,19 @@
         <v>87</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="O40" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>78</v>
@@ -6833,31 +6823,31 @@
         <v>78</v>
       </c>
       <c r="X40" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="Y40" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="Z40" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="AA40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF40" t="s" s="2">
         <v>238</v>
-      </c>
-      <c r="Y40" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="Z40" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="AA40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF40" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>76</v>
@@ -6872,7 +6862,7 @@
         <v>98</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>78</v>
@@ -6881,7 +6871,7 @@
         <v>78</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>78</v>
@@ -6889,10 +6879,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6918,29 +6908,29 @@
         <v>100</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q41" s="2"/>
       <c r="R41" t="s" s="2">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="S41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="T41" t="s" s="2">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="U41" t="s" s="2">
         <v>78</v>
@@ -6976,7 +6966,7 @@
         <v>78</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>76</v>
@@ -6991,7 +6981,7 @@
         <v>98</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>78</v>
@@ -7000,7 +6990,7 @@
         <v>78</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>78</v>
@@ -7008,10 +6998,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7034,16 +7024,16 @@
         <v>87</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>217</v>
+        <v>147</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7057,7 +7047,7 @@
         <v>78</v>
       </c>
       <c r="T42" t="s" s="2">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="U42" t="s" s="2">
         <v>78</v>
@@ -7093,7 +7083,7 @@
         <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>76</v>
@@ -7108,7 +7098,7 @@
         <v>98</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>78</v>
@@ -7117,7 +7107,7 @@
         <v>78</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>78</v>
@@ -7125,10 +7115,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7151,13 +7141,13 @@
         <v>87</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7208,7 +7198,7 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>76</v>
@@ -7223,7 +7213,7 @@
         <v>98</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>78</v>
@@ -7232,7 +7222,7 @@
         <v>78</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>78</v>
@@ -7240,10 +7230,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7266,16 +7256,16 @@
         <v>87</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="N44" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="L44" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7325,7 +7315,7 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
@@ -7340,7 +7330,7 @@
         <v>98</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>78</v>
@@ -7349,7 +7339,7 @@
         <v>78</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>78</v>
@@ -7357,13 +7347,13 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D45" t="s" s="2">
         <v>78</v>
@@ -7385,17 +7375,17 @@
         <v>87</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>78</v>
@@ -7444,7 +7434,7 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
@@ -7459,16 +7449,16 @@
         <v>98</v>
       </c>
       <c r="AK45" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="AL45" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="AL45" t="s" s="2">
+      <c r="AM45" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="AM45" t="s" s="2">
+      <c r="AN45" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="AN45" t="s" s="2">
-        <v>210</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>78</v>
@@ -7476,10 +7466,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7502,13 +7492,13 @@
         <v>78</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>217</v>
+        <v>147</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7559,7 +7549,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
@@ -7574,7 +7564,7 @@
         <v>78</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>78</v>
@@ -7591,14 +7581,14 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7620,13 +7610,13 @@
         <v>131</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>220</v>
+        <v>156</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7667,7 +7657,7 @@
         <v>134</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>78</v>
@@ -7676,7 +7666,7 @@
         <v>135</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>76</v>
@@ -7691,7 +7681,7 @@
         <v>137</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>78</v>
@@ -7708,10 +7698,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7737,16 +7727,16 @@
         <v>106</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="O48" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>78</v>
@@ -7771,31 +7761,31 @@
         <v>78</v>
       </c>
       <c r="X48" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="Z48" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF48" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="Y48" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="Z48" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="AA48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF48" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>76</v>
@@ -7810,7 +7800,7 @@
         <v>98</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>78</v>
@@ -7827,10 +7817,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7853,19 +7843,19 @@
         <v>87</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="O49" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>78</v>
@@ -7890,31 +7880,31 @@
         <v>78</v>
       </c>
       <c r="X49" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="Z49" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF49" t="s" s="2">
         <v>238</v>
-      </c>
-      <c r="Y49" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="Z49" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="AA49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF49" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>76</v>
@@ -7929,7 +7919,7 @@
         <v>98</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>78</v>
@@ -7938,7 +7928,7 @@
         <v>78</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>78</v>
@@ -7946,10 +7936,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7975,29 +7965,29 @@
         <v>100</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q50" s="2"/>
       <c r="R50" t="s" s="2">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="S50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="T50" t="s" s="2">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="U50" t="s" s="2">
         <v>78</v>
@@ -8033,7 +8023,7 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>76</v>
@@ -8048,7 +8038,7 @@
         <v>98</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>78</v>
@@ -8057,7 +8047,7 @@
         <v>78</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>78</v>
@@ -8065,10 +8055,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8091,16 +8081,16 @@
         <v>87</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>217</v>
+        <v>147</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8114,7 +8104,7 @@
         <v>78</v>
       </c>
       <c r="T51" t="s" s="2">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="U51" t="s" s="2">
         <v>78</v>
@@ -8150,7 +8140,7 @@
         <v>78</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>76</v>
@@ -8165,7 +8155,7 @@
         <v>98</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>78</v>
@@ -8174,7 +8164,7 @@
         <v>78</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>78</v>
@@ -8182,10 +8172,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8208,13 +8198,13 @@
         <v>87</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8265,7 +8255,7 @@
         <v>78</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>76</v>
@@ -8280,7 +8270,7 @@
         <v>98</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>78</v>
@@ -8289,7 +8279,7 @@
         <v>78</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>78</v>
@@ -8297,10 +8287,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8323,16 +8313,16 @@
         <v>87</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="N53" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="L53" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8382,7 +8372,7 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>76</v>
@@ -8397,7 +8387,7 @@
         <v>98</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>78</v>
@@ -8406,7 +8396,7 @@
         <v>78</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>78</v>
@@ -8414,13 +8404,13 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="D54" t="s" s="2">
         <v>78</v>
@@ -8442,17 +8432,17 @@
         <v>87</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>78</v>
@@ -8501,7 +8491,7 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>76</v>
@@ -8516,16 +8506,16 @@
         <v>98</v>
       </c>
       <c r="AK54" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="AL54" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="AL54" t="s" s="2">
+      <c r="AM54" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="AM54" t="s" s="2">
+      <c r="AN54" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>210</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>78</v>
@@ -8533,10 +8523,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8559,13 +8549,13 @@
         <v>78</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>217</v>
+        <v>147</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8616,7 +8606,7 @@
         <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>76</v>
@@ -8631,7 +8621,7 @@
         <v>78</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>78</v>
@@ -8648,14 +8638,14 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8677,13 +8667,13 @@
         <v>131</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>220</v>
+        <v>156</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8724,7 +8714,7 @@
         <v>134</v>
       </c>
       <c r="AC56" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AD56" t="s" s="2">
         <v>78</v>
@@ -8733,7 +8723,7 @@
         <v>135</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>76</v>
@@ -8748,7 +8738,7 @@
         <v>137</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>78</v>
@@ -8765,10 +8755,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8794,16 +8784,16 @@
         <v>106</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="O57" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>78</v>
@@ -8828,31 +8818,31 @@
         <v>78</v>
       </c>
       <c r="X57" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF57" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="Y57" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="Z57" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="AA57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF57" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>76</v>
@@ -8867,7 +8857,7 @@
         <v>98</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>78</v>
@@ -8884,10 +8874,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8910,19 +8900,19 @@
         <v>87</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="O58" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>78</v>
@@ -8947,31 +8937,31 @@
         <v>78</v>
       </c>
       <c r="X58" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF58" t="s" s="2">
         <v>238</v>
-      </c>
-      <c r="Y58" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="Z58" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="AA58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF58" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>76</v>
@@ -8986,7 +8976,7 @@
         <v>98</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>78</v>
@@ -8995,7 +8985,7 @@
         <v>78</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>78</v>
@@ -9003,10 +8993,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9029,13 +9019,13 @@
         <v>78</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>217</v>
+        <v>147</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9086,7 +9076,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>76</v>
@@ -9101,7 +9091,7 @@
         <v>78</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>78</v>
@@ -9118,14 +9108,14 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9147,13 +9137,13 @@
         <v>131</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>220</v>
+        <v>156</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9194,7 +9184,7 @@
         <v>134</v>
       </c>
       <c r="AC60" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AD60" t="s" s="2">
         <v>78</v>
@@ -9203,7 +9193,7 @@
         <v>135</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>76</v>
@@ -9218,7 +9208,7 @@
         <v>137</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>78</v>
@@ -9235,10 +9225,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9261,19 +9251,19 @@
         <v>87</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="N61" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="O61" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>332</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>78</v>
@@ -9322,7 +9312,7 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>76</v>
@@ -9337,7 +9327,7 @@
         <v>98</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>78</v>
@@ -9346,7 +9336,7 @@
         <v>78</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>78</v>
@@ -9354,10 +9344,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9380,13 +9370,13 @@
         <v>78</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>217</v>
+        <v>147</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9437,7 +9427,7 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>76</v>
@@ -9452,7 +9442,7 @@
         <v>78</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>78</v>
@@ -9469,14 +9459,14 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -9498,13 +9488,13 @@
         <v>131</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>220</v>
+        <v>156</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9545,7 +9535,7 @@
         <v>134</v>
       </c>
       <c r="AC63" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AD63" t="s" s="2">
         <v>78</v>
@@ -9554,7 +9544,7 @@
         <v>135</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>76</v>
@@ -9569,7 +9559,7 @@
         <v>137</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>78</v>
@@ -9586,10 +9576,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9615,23 +9605,23 @@
         <v>100</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="O64" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q64" s="2"/>
       <c r="R64" t="s" s="2">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="S64" t="s" s="2">
         <v>78</v>
@@ -9673,7 +9663,7 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>76</v>
@@ -9688,7 +9678,7 @@
         <v>98</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>78</v>
@@ -9697,7 +9687,7 @@
         <v>78</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>78</v>
@@ -9705,10 +9695,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9731,16 +9721,16 @@
         <v>87</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>217</v>
+        <v>147</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9790,7 +9780,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>76</v>
@@ -9805,7 +9795,7 @@
         <v>98</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>78</v>
@@ -9814,7 +9804,7 @@
         <v>78</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>78</v>
@@ -9822,10 +9812,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9851,21 +9841,21 @@
         <v>106</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q66" s="2"/>
       <c r="R66" t="s" s="2">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="S66" t="s" s="2">
         <v>78</v>
@@ -9907,7 +9897,7 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>76</v>
@@ -9922,7 +9912,7 @@
         <v>98</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>78</v>
@@ -9931,7 +9921,7 @@
         <v>78</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>78</v>
@@ -9939,10 +9929,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9965,17 +9955,17 @@
         <v>87</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>217</v>
+        <v>147</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>78</v>
@@ -10024,7 +10014,7 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>76</v>
@@ -10039,7 +10029,7 @@
         <v>98</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>78</v>
@@ -10048,7 +10038,7 @@
         <v>78</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>78</v>
@@ -10056,10 +10046,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10082,19 +10072,19 @@
         <v>87</v>
       </c>
       <c r="K68" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="N68" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="L68" t="s" s="2">
+      <c r="O68" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>380</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>78</v>
@@ -10143,7 +10133,7 @@
         <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>76</v>
@@ -10158,7 +10148,7 @@
         <v>98</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>78</v>
@@ -10167,7 +10157,7 @@
         <v>78</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>78</v>
@@ -10175,10 +10165,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10201,19 +10191,19 @@
         <v>87</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>217</v>
+        <v>147</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="O69" t="s" s="2">
         <v>386</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>389</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>78</v>
@@ -10262,7 +10252,7 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>76</v>
@@ -10277,7 +10267,7 @@
         <v>98</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>78</v>
@@ -10286,7 +10276,7 @@
         <v>78</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>78</v>
@@ -10294,10 +10284,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10323,29 +10313,29 @@
         <v>100</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q70" s="2"/>
       <c r="R70" t="s" s="2">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="S70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="T70" t="s" s="2">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="U70" t="s" s="2">
         <v>78</v>
@@ -10381,7 +10371,7 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>76</v>
@@ -10396,7 +10386,7 @@
         <v>98</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>78</v>
@@ -10405,7 +10395,7 @@
         <v>78</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>78</v>
@@ -10413,10 +10403,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10439,16 +10429,16 @@
         <v>87</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>217</v>
+        <v>147</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10462,7 +10452,7 @@
         <v>78</v>
       </c>
       <c r="T71" t="s" s="2">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="U71" t="s" s="2">
         <v>78</v>
@@ -10498,7 +10488,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>76</v>
@@ -10513,7 +10503,7 @@
         <v>98</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>78</v>
@@ -10522,7 +10512,7 @@
         <v>78</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>78</v>
@@ -10530,10 +10520,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10556,13 +10546,13 @@
         <v>87</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10613,7 +10603,7 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>76</v>
@@ -10628,7 +10618,7 @@
         <v>98</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="AL72" t="s" s="2">
         <v>78</v>
@@ -10637,7 +10627,7 @@
         <v>78</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>78</v>
@@ -10645,10 +10635,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10671,16 +10661,16 @@
         <v>87</v>
       </c>
       <c r="K73" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="N73" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="L73" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10730,7 +10720,7 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>76</v>
@@ -10745,7 +10735,7 @@
         <v>98</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="AL73" t="s" s="2">
         <v>78</v>
@@ -10754,7 +10744,7 @@
         <v>78</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>78</v>
@@ -10762,10 +10752,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10788,26 +10778,26 @@
         <v>87</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="O74" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="P74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q74" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="N74" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="P74" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q74" t="s" s="2">
-        <v>407</v>
-      </c>
       <c r="R74" t="s" s="2">
         <v>78</v>
       </c>
@@ -10851,7 +10841,7 @@
         <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>76</v>
@@ -10866,13 +10856,13 @@
         <v>98</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>78</v>
@@ -10883,10 +10873,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10909,19 +10899,19 @@
         <v>87</v>
       </c>
       <c r="K75" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="N75" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="L75" t="s" s="2">
+      <c r="O75" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>415</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>78</v>
@@ -10970,7 +10960,7 @@
         <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>76</v>
@@ -10985,16 +10975,16 @@
         <v>98</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>78</v>
@@ -11002,10 +10992,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11028,19 +11018,19 @@
         <v>87</v>
       </c>
       <c r="K76" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="N76" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="L76" t="s" s="2">
+      <c r="O76" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>424</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>78</v>
@@ -11089,7 +11079,7 @@
         <v>78</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>76</v>
@@ -11104,16 +11094,16 @@
         <v>98</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>78</v>
@@ -11121,10 +11111,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11150,16 +11140,16 @@
         <v>106</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="O77" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>432</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>78</v>
@@ -11184,13 +11174,13 @@
         <v>78</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>78</v>
@@ -11208,7 +11198,7 @@
         <v>78</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>76</v>
@@ -11223,16 +11213,16 @@
         <v>98</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>78</v>
@@ -11240,10 +11230,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11266,19 +11256,19 @@
         <v>87</v>
       </c>
       <c r="K78" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="N78" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="L78" t="s" s="2">
+      <c r="O78" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>443</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>78</v>
@@ -11327,7 +11317,7 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>76</v>
@@ -11342,27 +11332,27 @@
         <v>98</v>
       </c>
       <c r="AK78" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN78" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AO78" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="AL78" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="AM78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN78" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="AO78" t="s" s="2">
-        <v>447</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11385,19 +11375,19 @@
         <v>87</v>
       </c>
       <c r="K79" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="N79" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="L79" t="s" s="2">
+      <c r="O79" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>78</v>
@@ -11446,7 +11436,7 @@
         <v>78</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>76</v>
@@ -11461,16 +11451,16 @@
         <v>98</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>78</v>
@@ -11478,10 +11468,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11504,19 +11494,19 @@
         <v>87</v>
       </c>
       <c r="K80" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="L80" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="N80" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="L80" t="s" s="2">
+      <c r="O80" t="s" s="2">
         <v>458</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>78</v>
@@ -11565,7 +11555,7 @@
         <v>78</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>76</v>
@@ -11580,16 +11570,16 @@
         <v>98</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>78</v>
@@ -11597,10 +11587,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11623,17 +11613,17 @@
         <v>78</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" t="s" s="2">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>78</v>
@@ -11658,13 +11648,13 @@
         <v>78</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>78</v>
@@ -11682,7 +11672,7 @@
         <v>78</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>76</v>
@@ -11697,16 +11687,16 @@
         <v>98</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>78</v>
@@ -11714,10 +11704,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11740,19 +11730,19 @@
         <v>78</v>
       </c>
       <c r="K82" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="L82" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="N82" t="s" s="2">
         <v>475</v>
       </c>
-      <c r="L82" t="s" s="2">
+      <c r="O82" t="s" s="2">
         <v>476</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>479</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>78</v>
@@ -11801,7 +11791,7 @@
         <v>78</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>76</v>
@@ -11816,16 +11806,16 @@
         <v>98</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>78</v>
@@ -11833,10 +11823,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11859,19 +11849,19 @@
         <v>78</v>
       </c>
       <c r="K83" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="N83" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="L83" t="s" s="2">
+      <c r="O83" t="s" s="2">
         <v>484</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>487</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>78</v>
@@ -11920,7 +11910,7 @@
         <v>78</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>76</v>
@@ -11935,16 +11925,16 @@
         <v>98</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>78</v>
@@ -11952,10 +11942,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11978,19 +11968,19 @@
         <v>78</v>
       </c>
       <c r="K84" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="N84" t="s" s="2">
         <v>491</v>
       </c>
-      <c r="L84" t="s" s="2">
+      <c r="O84" t="s" s="2">
         <v>492</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>495</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>78</v>
@@ -12039,7 +12029,7 @@
         <v>78</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>76</v>
@@ -12051,13 +12041,13 @@
         <v>78</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>78</v>
@@ -12071,10 +12061,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12097,13 +12087,13 @@
         <v>78</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>217</v>
+        <v>147</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -12154,7 +12144,7 @@
         <v>78</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>76</v>
@@ -12169,7 +12159,7 @@
         <v>78</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AL85" t="s" s="2">
         <v>78</v>
@@ -12186,14 +12176,14 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
@@ -12215,13 +12205,13 @@
         <v>131</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>220</v>
+        <v>156</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -12271,7 +12261,7 @@
         <v>78</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>76</v>
@@ -12286,7 +12276,7 @@
         <v>137</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AL86" t="s" s="2">
         <v>78</v>
@@ -12303,14 +12293,14 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -12332,16 +12322,16 @@
         <v>131</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>78</v>
@@ -12390,7 +12380,7 @@
         <v>78</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>76</v>
@@ -12422,10 +12412,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12448,17 +12438,17 @@
         <v>78</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>78</v>
@@ -12483,13 +12473,13 @@
         <v>78</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>78</v>
@@ -12507,7 +12497,7 @@
         <v>78</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>76</v>
@@ -12522,16 +12512,16 @@
         <v>98</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>78</v>
@@ -12539,10 +12529,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12565,17 +12555,17 @@
         <v>78</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>78</v>
@@ -12624,7 +12614,7 @@
         <v>78</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>76</v>
@@ -12639,16 +12629,16 @@
         <v>98</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>78</v>
@@ -12656,10 +12646,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12682,19 +12672,19 @@
         <v>78</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>78</v>
@@ -12743,7 +12733,7 @@
         <v>78</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>76</v>
@@ -12758,16 +12748,16 @@
         <v>98</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>78</v>
@@ -12775,10 +12765,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12801,17 +12791,17 @@
         <v>78</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" t="s" s="2">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>78</v>
@@ -12860,7 +12850,7 @@
         <v>78</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>76</v>
@@ -12875,16 +12865,16 @@
         <v>98</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>78</v>
@@ -12892,10 +12882,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12921,14 +12911,14 @@
         <v>106</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" t="s" s="2">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>78</v>
@@ -12953,13 +12943,13 @@
         <v>78</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>78</v>
@@ -12977,7 +12967,7 @@
         <v>78</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>76</v>
@@ -12992,16 +12982,16 @@
         <v>98</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>78</v>
@@ -13009,10 +12999,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13035,17 +13025,17 @@
         <v>78</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" t="s" s="2">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>78</v>
@@ -13094,7 +13084,7 @@
         <v>78</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>76</v>
@@ -13103,22 +13093,22 @@
         <v>86</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="AJ93" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>78</v>
@@ -13126,10 +13116,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13152,13 +13142,13 @@
         <v>78</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -13209,7 +13199,7 @@
         <v>78</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>76</v>
@@ -13224,10 +13214,10 @@
         <v>98</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>78</v>
@@ -13241,10 +13231,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13267,19 +13257,19 @@
         <v>78</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="L95" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="M95" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="O95" t="s" s="2">
         <v>543</v>
-      </c>
-      <c r="M95" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="O95" t="s" s="2">
-        <v>546</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>78</v>
@@ -13328,7 +13318,7 @@
         <v>78</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>76</v>
@@ -13343,10 +13333,10 @@
         <v>98</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>78</v>
@@ -13360,10 +13350,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13386,13 +13376,13 @@
         <v>78</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>217</v>
+        <v>147</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -13443,7 +13433,7 @@
         <v>78</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>76</v>
@@ -13458,7 +13448,7 @@
         <v>78</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AL96" t="s" s="2">
         <v>78</v>
@@ -13475,14 +13465,14 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -13504,13 +13494,13 @@
         <v>131</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>220</v>
+        <v>156</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -13560,7 +13550,7 @@
         <v>78</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>76</v>
@@ -13575,7 +13565,7 @@
         <v>137</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AL97" t="s" s="2">
         <v>78</v>
@@ -13592,14 +13582,14 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
@@ -13621,16 +13611,16 @@
         <v>131</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>78</v>
@@ -13679,7 +13669,7 @@
         <v>78</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>76</v>
@@ -13711,10 +13701,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13737,19 +13727,19 @@
         <v>78</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L99" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="M99" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="N99" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="O99" t="s" s="2">
         <v>553</v>
-      </c>
-      <c r="M99" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>555</v>
-      </c>
-      <c r="O99" t="s" s="2">
-        <v>556</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>78</v>
@@ -13798,7 +13788,7 @@
         <v>78</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>86</v>
@@ -13813,16 +13803,16 @@
         <v>98</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>78</v>
@@ -13830,10 +13820,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13856,19 +13846,19 @@
         <v>78</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="L100" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="M100" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="O100" t="s" s="2">
         <v>561</v>
-      </c>
-      <c r="M100" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>564</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>78</v>
@@ -13917,7 +13907,7 @@
         <v>78</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>76</v>
@@ -13932,16 +13922,16 @@
         <v>98</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>78</v>
@@ -13949,14 +13939,14 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
@@ -13975,16 +13965,16 @@
         <v>78</v>
       </c>
       <c r="K101" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="L101" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="M101" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="N101" t="s" s="2">
         <v>570</v>
-      </c>
-      <c r="L101" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="M101" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>573</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -14034,7 +14024,7 @@
         <v>78</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>76</v>
@@ -14049,16 +14039,16 @@
         <v>98</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>78</v>
@@ -14066,10 +14056,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14092,19 +14082,19 @@
         <v>87</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="L102" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="M102" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="N102" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="O102" t="s" s="2">
         <v>577</v>
-      </c>
-      <c r="M102" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="O102" t="s" s="2">
-        <v>580</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>78</v>
@@ -14153,7 +14143,7 @@
         <v>78</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>76</v>
@@ -14168,10 +14158,10 @@
         <v>98</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>78</v>
@@ -14185,10 +14175,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14211,19 +14201,19 @@
         <v>87</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="L103" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="M103" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="O103" t="s" s="2">
         <v>583</v>
-      </c>
-      <c r="M103" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="O103" t="s" s="2">
-        <v>586</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>78</v>
@@ -14272,7 +14262,7 @@
         <v>78</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>76</v>
@@ -14287,10 +14277,10 @@
         <v>98</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>78</v>
@@ -14304,10 +14294,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14330,13 +14320,13 @@
         <v>78</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>217</v>
+        <v>147</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -14387,7 +14377,7 @@
         <v>78</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>76</v>
@@ -14402,7 +14392,7 @@
         <v>78</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AL104" t="s" s="2">
         <v>78</v>
@@ -14419,14 +14409,14 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
@@ -14448,13 +14438,13 @@
         <v>131</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>220</v>
+        <v>156</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -14504,7 +14494,7 @@
         <v>78</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>76</v>
@@ -14519,7 +14509,7 @@
         <v>137</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AL105" t="s" s="2">
         <v>78</v>
@@ -14536,14 +14526,14 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
@@ -14565,16 +14555,16 @@
         <v>131</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>78</v>
@@ -14623,7 +14613,7 @@
         <v>78</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>76</v>
@@ -14655,10 +14645,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14681,16 +14671,16 @@
         <v>87</v>
       </c>
       <c r="K107" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="L107" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="M107" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="N107" t="s" s="2">
         <v>592</v>
-      </c>
-      <c r="L107" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="M107" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>595</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -14740,7 +14730,7 @@
         <v>78</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>86</v>
@@ -14755,16 +14745,16 @@
         <v>98</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>78</v>
@@ -14772,10 +14762,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14801,10 +14791,10 @@
         <v>106</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -14831,13 +14821,13 @@
         <v>78</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>78</v>
@@ -14855,7 +14845,7 @@
         <v>78</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>86</v>
@@ -14870,10 +14860,10 @@
         <v>98</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>78</v>

--- a/testbuild/StructureDefinition-no-basis-Patient.xlsx
+++ b/testbuild/StructureDefinition-no-basis-Patient.xlsx
@@ -571,7 +571,7 @@
     <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
   </si>
   <si>
-    <t>urn:iso:std:iso:3166</t>
+    <t>http://hl7.org/fhir/ValueSet/iso3166-1-2</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
